--- a/A2259C_C.xlsx
+++ b/A2259C_C.xlsx
@@ -1,32 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myrp-my.sharepoint.com/personal/paul_z_chen_rp_edu_sg/Documents/A2259C/A2295C graded assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_A7DBE5189BEB4C903936263C93EB004933C0224B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B625FA-1BE0-4321-B68D-1924BEF4327F}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_A7DBE5189BEB4C903936263C93EB004933C0224B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DF209CE-0219-4F2C-99A0-AAAE9D23371F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
     <sheet name="Data1" sheetId="2" r:id="rId2"/>
-    <sheet name="Data2" sheetId="3" r:id="rId3"/>
-    <sheet name="Data3" sheetId="4" r:id="rId4"/>
-    <sheet name="Questions_Data1" sheetId="5" r:id="rId5"/>
-    <sheet name="Questions_Data2" sheetId="6" r:id="rId6"/>
+    <sheet name="Questions_Data1" sheetId="5" r:id="rId3"/>
+    <sheet name="Data2" sheetId="3" r:id="rId4"/>
+    <sheet name="Questions_Data2" sheetId="6" r:id="rId5"/>
+    <sheet name="Data3" sheetId="4" r:id="rId6"/>
     <sheet name="Questions_Data3" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="221">
   <si>
     <t>Outlet_ID</t>
   </si>
@@ -737,6 +750,9 @@
       </rPr>
       <t>2</t>
     </r>
+  </si>
+  <si>
+    <t>Briefly discuss one limitation of relying on generative AI to solve this question.</t>
   </si>
 </sst>
 </file>
@@ -1744,6 +1760,126 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2164,815 +2300,6 @@
       </c>
       <c r="C38">
         <v>271.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C72"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2">
-        <v>45.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3">
-        <v>33.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4">
-        <v>41.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6">
-        <v>29.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7">
-        <v>40.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8">
-        <v>41.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9">
-        <v>55.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10">
-        <v>38.200000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11">
-        <v>52.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14">
-        <v>41.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15">
-        <v>45.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16">
-        <v>47.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>127</v>
-      </c>
-      <c r="B18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18">
-        <v>56.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19">
-        <v>34.299999999999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22">
-        <v>52.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23">
-        <v>46.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24">
-        <v>45.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>134</v>
-      </c>
-      <c r="B25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26">
-        <v>34.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28">
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29">
-        <v>53.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30">
-        <v>43.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31">
-        <v>44.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>141</v>
-      </c>
-      <c r="B32" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>142</v>
-      </c>
-      <c r="B33" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33">
-        <v>48.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>143</v>
-      </c>
-      <c r="B34" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34">
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>144</v>
-      </c>
-      <c r="B35" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35">
-        <v>54.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>146</v>
-      </c>
-      <c r="B37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C37">
-        <v>42.3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>147</v>
-      </c>
-      <c r="B38" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38">
-        <v>51.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>148</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>149</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>150</v>
-      </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41">
-        <v>69.618390330532606</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42">
-        <v>38.200000000000003</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>152</v>
-      </c>
-      <c r="B43" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43">
-        <v>37.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>153</v>
-      </c>
-      <c r="B44" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44">
-        <v>51.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>154</v>
-      </c>
-      <c r="B45" t="s">
-        <v>113</v>
-      </c>
-      <c r="C45">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>155</v>
-      </c>
-      <c r="B46" t="s">
-        <v>111</v>
-      </c>
-      <c r="C46">
-        <v>46.6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>156</v>
-      </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47">
-        <v>40.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>157</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>158</v>
-      </c>
-      <c r="B49" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49">
-        <v>35.700000000000003</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>159</v>
-      </c>
-      <c r="B50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>160</v>
-      </c>
-      <c r="B51" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51">
-        <v>43.2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>161</v>
-      </c>
-      <c r="B52" t="s">
-        <v>113</v>
-      </c>
-      <c r="C52">
-        <v>36.700000000000003</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>163</v>
-      </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54">
-        <v>54.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>164</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>165</v>
-      </c>
-      <c r="B56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C56">
-        <v>36.9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>166</v>
-      </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57">
-        <v>46.3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>167</v>
-      </c>
-      <c r="B58" t="s">
-        <v>111</v>
-      </c>
-      <c r="C58">
-        <v>39.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>168</v>
-      </c>
-      <c r="B59" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59">
-        <v>52.1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>169</v>
-      </c>
-      <c r="B60" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60">
-        <v>34.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>170</v>
-      </c>
-      <c r="B61" t="s">
-        <v>111</v>
-      </c>
-      <c r="C61">
-        <v>53.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>171</v>
-      </c>
-      <c r="B62" t="s">
-        <v>113</v>
-      </c>
-      <c r="C62">
-        <v>42.4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>172</v>
-      </c>
-      <c r="B63" t="s">
-        <v>113</v>
-      </c>
-      <c r="C63">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>173</v>
-      </c>
-      <c r="B64" t="s">
-        <v>113</v>
-      </c>
-      <c r="C64">
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>174</v>
-      </c>
-      <c r="B65" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65">
-        <v>42.1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>175</v>
-      </c>
-      <c r="B66" t="s">
-        <v>111</v>
-      </c>
-      <c r="C66">
-        <v>40.200000000000003</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>176</v>
-      </c>
-      <c r="B67" t="s">
-        <v>113</v>
-      </c>
-      <c r="C67">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>177</v>
-      </c>
-      <c r="B68" t="s">
-        <v>111</v>
-      </c>
-      <c r="C68">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>178</v>
-      </c>
-      <c r="B69" t="s">
-        <v>111</v>
-      </c>
-      <c r="C69">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>179</v>
-      </c>
-      <c r="B70" t="s">
-        <v>113</v>
-      </c>
-      <c r="C70">
-        <v>45.4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>180</v>
-      </c>
-      <c r="B71" t="s">
-        <v>109</v>
-      </c>
-      <c r="C71">
-        <v>53.9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>181</v>
-      </c>
-      <c r="B72" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72">
-        <v>33.1</v>
       </c>
     </row>
   </sheetData>
@@ -2988,126 +2315,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3226,9 +2433,818 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C72"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10">
+        <v>38.200000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11">
+        <v>52.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19">
+        <v>34.299999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31">
+        <v>44.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41">
+        <v>69.618390330532606</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42">
+        <v>38.200000000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>156</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>157</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>158</v>
+      </c>
+      <c r="B49" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49">
+        <v>35.700000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>163</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59">
+        <v>52.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" t="s">
+        <v>113</v>
+      </c>
+      <c r="C62">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>172</v>
+      </c>
+      <c r="B63" t="s">
+        <v>113</v>
+      </c>
+      <c r="C63">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>173</v>
+      </c>
+      <c r="B64" t="s">
+        <v>113</v>
+      </c>
+      <c r="C64">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>174</v>
+      </c>
+      <c r="B65" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>175</v>
+      </c>
+      <c r="B66" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66">
+        <v>40.200000000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>176</v>
+      </c>
+      <c r="B67" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>177</v>
+      </c>
+      <c r="B68" t="s">
+        <v>111</v>
+      </c>
+      <c r="C68">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" t="s">
+        <v>111</v>
+      </c>
+      <c r="C69">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>179</v>
+      </c>
+      <c r="B70" t="s">
+        <v>113</v>
+      </c>
+      <c r="C70">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>180</v>
+      </c>
+      <c r="B71" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>181</v>
+      </c>
+      <c r="B72" t="s">
+        <v>109</v>
+      </c>
+      <c r="C72">
+        <v>33.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 Official (Closed) \ Sensitive Normal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
@@ -3344,6 +3360,15 @@
         <v>208</v>
       </c>
       <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
